--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2021_T4_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2021_T4_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>67</t>
+    <t>61</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,37 +57,37 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.343</t>
+    <t>0.377</t>
+  </si>
+  <si>
+    <t>(0.063)</t>
+  </si>
+  <si>
+    <t>0.574</t>
+  </si>
+  <si>
+    <t>(0.064)</t>
+  </si>
+  <si>
+    <t>0.279</t>
   </si>
   <si>
     <t>(0.058)</t>
   </si>
   <si>
-    <t>0.522</t>
-  </si>
-  <si>
-    <t>(0.061)</t>
-  </si>
-  <si>
-    <t>0.254</t>
-  </si>
-  <si>
-    <t>(0.054)</t>
-  </si>
-  <si>
-    <t>1.612</t>
-  </si>
-  <si>
-    <t>(0.602)</t>
-  </si>
-  <si>
-    <t>1.209</t>
-  </si>
-  <si>
-    <t>(0.206)</t>
-  </si>
-  <si>
-    <t>(0.081)</t>
+    <t>1.770</t>
+  </si>
+  <si>
+    <t>(0.658)</t>
+  </si>
+  <si>
+    <t>1.328</t>
+  </si>
+  <si>
+    <t>(0.220)</t>
+  </si>
+  <si>
+    <t>(0.088)</t>
   </si>
   <si>
     <t>49</t>
@@ -132,7 +132,7 @@
     <t>(0.282)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -144,22 +144,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.269***</t>
-  </si>
-  <si>
-    <t>0.355***</t>
-  </si>
-  <si>
-    <t>0.379***</t>
-  </si>
-  <si>
-    <t>0.898</t>
-  </si>
-  <si>
-    <t>3.220***</t>
-  </si>
-  <si>
-    <t>1.289***</t>
+    <t>0.235**</t>
+  </si>
+  <si>
+    <t>0.304***</t>
+  </si>
+  <si>
+    <t>0.354***</t>
+  </si>
+  <si>
+    <t>0.740</t>
+  </si>
+  <si>
+    <t>3.101***</t>
+  </si>
+  <si>
+    <t>1.256***</t>
   </si>
 </sst>
 </file>
